--- a/output/pdf_financials_xlsx/BDI.xlsx
+++ b/output/pdf_financials_xlsx/BDI.xlsx
@@ -1334,7 +1334,7 @@
         <v>35.038</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>8.4</v>
+        <v>-8.4</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>-64.15000000000001</v>
@@ -1642,7 +1642,7 @@
         <v>35.038</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>8.4</v>
+        <v>-8.4</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-64.15000000000001</v>
@@ -1826,7 +1826,7 @@
         <v>35.038</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>8.4</v>
+        <v>-8.4</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-64.15000000000001</v>
@@ -2164,7 +2164,7 @@
         <v>35.038</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>8.4</v>
+        <v>-8.4</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-64.15000000000001</v>
@@ -2286,7 +2286,7 @@
         <v>36.745</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>65.232</v>
+        <v>48.432</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-11.636</v>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-0</v>
@@ -3391,13 +3391,13 @@
         <v>1.846</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0</v>
+        <v>0.874</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.874</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>21.941</v>
+        <v>8.066000000000001</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>7.477</v>
@@ -3409,7 +3409,7 @@
         <v>5.401</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.482</v>
+        <v>6.032</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>6.237</v>
@@ -3445,11 +3445,15 @@
           <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
-      <c r="B49" s="3" t="n">
-        <v>1.846</v>
-      </c>
-      <c r="C49" s="3" t="n">
-        <v>0.874</v>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D49" s="3" t="n">
         <v>13.427</v>
@@ -4182,10 +4186,10 @@
         <v>0</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>0</v>
+        <v>9.821</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>52.725</v>
+        <v>12.064</v>
       </c>
       <c r="F61" s="3" t="n">
         <v>0</v>
@@ -6402,7 +6406,7 @@
         <v>35.038</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>8.4</v>
+        <v>-8.4</v>
       </c>
       <c r="J99" s="3" t="n">
         <v>-64.15000000000001</v>
@@ -8883,7 +8887,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -13305,7 +13309,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -18027,7 +18031,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -22292,7 +22296,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -28912,7 +28916,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E209" s="5" t="n">
@@ -36340,7 +36344,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -36546,7 +36550,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherNonCurrentAssets</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -54604,7 +54608,7 @@
         </is>
       </c>
       <c r="L468" s="5" t="n">
-        <v>8.4</v>
+        <v>-8.4</v>
       </c>
       <c r="M468" s="5" t="n">
         <v>-64.15000000000001</v>
@@ -76251,7 +76255,7 @@
         </is>
       </c>
       <c r="L685" s="5" t="n">
-        <v>8.4</v>
+        <v>-8.4</v>
       </c>
       <c r="M685" s="5" t="n">
         <v>-64.15000000000001</v>

--- a/output/pdf_financials_xlsx/BDI.xlsx
+++ b/output/pdf_financials_xlsx/BDI.xlsx
@@ -3391,13 +3391,13 @@
         <v>1.846</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.874</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.874</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>8.066000000000001</v>
+        <v>21.941</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>7.477</v>
@@ -3409,7 +3409,7 @@
         <v>5.401</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>6.032</v>
+        <v>0.482</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>6.237</v>
@@ -3445,15 +3445,11 @@
           <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="3" t="n">
+        <v>1.846</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>0.874</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>13.427</v>
@@ -4186,10 +4182,10 @@
         <v>0</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>9.821</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>12.064</v>
+        <v>52.725</v>
       </c>
       <c r="F61" s="3" t="n">
         <v>0</v>
@@ -8887,7 +8883,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -13309,7 +13305,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -18031,7 +18027,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -22296,7 +22292,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -28916,7 +28912,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E209" s="5" t="n">
@@ -36344,7 +36340,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -36550,7 +36546,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>OtherNonCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">

--- a/output/pdf_financials_xlsx/BDI.xlsx
+++ b/output/pdf_financials_xlsx/BDI.xlsx
@@ -2209,19 +2209,19 @@
         <v>0.991</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1.547</v>
+        <v>21.076</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1.415</v>
+        <v>28.7</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.879</v>
+        <v>35.544</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1.46</v>
+        <v>51.354</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>1.707</v>
+        <v>54.786</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>56.832</v>
@@ -2269,7 +2269,7 @@
         <v>20.117</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>20.376</v>
+        <v>39.905</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>48.273</v>
+        <v>82.938</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>54.676</v>
+        <v>104.57</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>36.745</v>
+        <v>89.824</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>48.432</v>
@@ -6439,25 +6439,25 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.991</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>21.076</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>28.7</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>35.544</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>51.354</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>54.786</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>56.832</v>
@@ -47734,7 +47734,11 @@
           <t>Additions to intangible assets (notes 10 and 26)</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E397" t="inlineStr">
         <is>
           <t>-</t>
@@ -50479,7 +50483,11 @@
           <t>Additions to intangible assets (notes 9 and 25)</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
           <t>-</t>
@@ -52603,7 +52611,11 @@
           <t>Additions to intangible assets (notes 10 and 27)</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
           <t>-</t>
@@ -55559,7 +55571,11 @@
           <t>Additions to intangible assets (note 8 and 25)</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
           <t>-</t>
@@ -57149,7 +57165,11 @@
           <t>Additions to intangible assets (note 8 and 26)</t>
         </is>
       </c>
-      <c r="D494" t="inlineStr"/>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E494" t="inlineStr">
         <is>
           <t>-</t>
@@ -60119,7 +60139,11 @@
           <t>Depreciation of property and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D524" t="inlineStr"/>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E524" t="inlineStr">
         <is>
           <t>-</t>
@@ -60218,7 +60242,7 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -62828,7 +62852,11 @@
           <t>Depreciation of property and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D551" t="inlineStr"/>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E551" t="inlineStr">
         <is>
           <t>-</t>
@@ -62929,7 +62957,7 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -64917,7 +64945,11 @@
           <t>Depreciation of property and equipment (note 4)</t>
         </is>
       </c>
-      <c r="D572" t="inlineStr"/>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E572" t="inlineStr">
         <is>
           <t>-</t>
@@ -65018,7 +65050,7 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
@@ -67929,7 +67961,11 @@
           <t>Depreciation of property and equipment (note 5)</t>
         </is>
       </c>
-      <c r="D602" t="inlineStr"/>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E602" t="inlineStr">
         <is>
           <t>-</t>
@@ -68030,7 +68066,7 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
@@ -70959,7 +70995,7 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
@@ -73377,7 +73413,7 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E656" s="5" t="n">
@@ -74181,7 +74217,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D664" t="inlineStr"/>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E664" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BDI.xlsx
+++ b/output/pdf_financials_xlsx/BDI.xlsx
@@ -4081,34 +4081,34 @@
         <v>10.079</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>42.484</v>
+        <v>8.726000000000001</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>43.764</v>
+        <v>0</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>18.167</v>
+        <v>0</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>18.882</v>
+        <v>0</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>18.103</v>
+        <v>0</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>20.85</v>
+        <v>0</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>32.727</v>
+        <v>0</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>31.941</v>
+        <v>0</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>31.295</v>
+        <v>0</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>78.327</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -4367,46 +4367,46 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>8.624000000000001</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>5.758</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>7.679</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>17.719</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>9.503</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>15.015</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>11.293</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>15.674</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>11.242</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>9.901999999999999</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>8.879</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>10.453</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>13.062</v>
       </c>
     </row>
     <row r="65">
@@ -4568,19 +4568,19 @@
         <v>0</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>20.868</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>15.623</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>19.936</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>12.937</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>24.15</v>
       </c>
     </row>
     <row r="68">
@@ -6851,19 +6851,19 @@
         <v>0.372</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0.9389999999999999</v>
+        <v>1.972</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>1.843</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>3.321</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>3.035</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>5.249</v>
       </c>
       <c r="I107" s="3" t="n">
         <v>4.645</v>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -13816,7 +13816,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -18433,7 +18433,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -20605,7 +20605,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -22597,7 +22597,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -24403,7 +24403,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -60040,7 +60040,11 @@
           <t>Share based compensation expense (note 18)</t>
         </is>
       </c>
-      <c r="D523" t="inlineStr"/>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E523" t="inlineStr">
         <is>
           <t>-</t>
@@ -61644,7 +61648,11 @@
           <t>Share based compensation expense (note 19)</t>
         </is>
       </c>
-      <c r="D539" t="inlineStr"/>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E539" t="inlineStr">
         <is>
           <t>-</t>
@@ -63458,7 +63466,11 @@
           <t>Share based compensation expense (note 18)</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr"/>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E557" t="inlineStr">
         <is>
           <t>-</t>
@@ -65448,7 +65460,11 @@
           <t>Share-based compensation expense (note 23)</t>
         </is>
       </c>
-      <c r="D577" t="inlineStr"/>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E577" t="inlineStr">
         <is>
           <t>-</t>
@@ -68464,7 +68480,11 @@
           <t>Share-based compensation expense (note 25)</t>
         </is>
       </c>
-      <c r="D607" t="inlineStr"/>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E607" t="inlineStr">
         <is>
           <t>-</t>
@@ -71397,7 +71417,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D636" t="inlineStr"/>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E636" t="inlineStr">
         <is>
           <t>-</t>
@@ -73716,7 +73740,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D659" t="inlineStr"/>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E659" s="5" t="n">
         <v>2.44</v>
       </c>
